--- a/artfynd/A 21744-2023 artfynd.xlsx
+++ b/artfynd/A 21744-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21744-2023 artfynd.xlsx
+++ b/artfynd/A 21744-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113679724</v>
       </c>
       <c r="B2" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,12 +770,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 21744-2023 artfynd.xlsx
+++ b/artfynd/A 21744-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679724</v>
       </c>
       <c r="B2" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21744-2023 artfynd.xlsx
+++ b/artfynd/A 21744-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679724</v>
       </c>
       <c r="B2" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21744-2023 artfynd.xlsx
+++ b/artfynd/A 21744-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679724</v>
       </c>
       <c r="B2" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21744-2023 artfynd.xlsx
+++ b/artfynd/A 21744-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679724</v>
       </c>
       <c r="B2" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21744-2023 artfynd.xlsx
+++ b/artfynd/A 21744-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679724</v>
       </c>
       <c r="B2" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21744-2023 artfynd.xlsx
+++ b/artfynd/A 21744-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679724</v>
       </c>
       <c r="B2" t="n">
-        <v>80394</v>
+        <v>80397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
